--- a/artfynd/A 73761-2021 artfynd.xlsx
+++ b/artfynd/A 73761-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 73761-2021 artfynd.xlsx
+++ b/artfynd/A 73761-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>96736074</v>
+        <v>96736156</v>
       </c>
       <c r="B2" t="n">
-        <v>90005</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1339</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>634874.3519818332</v>
+        <v>634722</v>
       </c>
       <c r="R2" t="n">
-        <v>6699597.082524561</v>
+        <v>6699681</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,21 +743,11 @@
           <t>2021-10-18</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-10-18</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -779,7 +764,7 @@
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>brunmurken granlåga</t>
+          <t>låga</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -797,37 +782,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>102249955</v>
+        <v>102249942</v>
       </c>
       <c r="B3" t="n">
-        <v>96312</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219798</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -837,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>634657.7223021489</v>
+        <v>634763</v>
       </c>
       <c r="R3" t="n">
-        <v>6700308.928887788</v>
+        <v>6699652</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -870,19 +850,14 @@
           <t>2022-07-12</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-07-12</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På gammal tallåga</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -913,50 +888,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>102249952</v>
+        <v>96736011</v>
       </c>
       <c r="B4" t="n">
-        <v>96251</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219790</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Östanås, Upl</t>
+          <t>öst om Östanås, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>634679.6390727247</v>
+        <v>634747</v>
       </c>
       <c r="R4" t="n">
-        <v>6700052.158978951</v>
+        <v>6699646</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -983,22 +953,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-07-12</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-07-12</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-15</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1009,35 +969,36 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>örtrik äldre granskog</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>granlåga</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Johan Lilja</t>
+          <t>Olof Hedgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Johan Lilja</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>Länsstyrelsen i Uppsala län, områdesskydd</t>
-        </is>
-      </c>
+          <t>Olof Hedgren</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>102249942</v>
+        <v>96736079</v>
       </c>
       <c r="B5" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1045,37 +1006,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>53</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Östanås, Upl</t>
+          <t>öst om Östanås, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>634762.382742792</v>
+        <v>634836</v>
       </c>
       <c r="R5" t="n">
-        <v>6699651.2688645</v>
+        <v>6699581</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1099,27 +1060,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-07-12</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-18</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-07-12</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På gammal tallåga</t>
+          <t>2021-10-18</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1130,23 +1076,1070 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>örtrik äldre granskog</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>granlåga</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
+          <t>Olof Hedgren</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Olof Hedgren</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>96736081</v>
+      </c>
+      <c r="B6" t="n">
+        <v>92369</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>öst om Östanås, Upl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>634836</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6699581</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Tolfta</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2021-10-18</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2021-10-18</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>örtrik äldre granskog</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>granlåga</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Olof Hedgren</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Olof Hedgren</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>96736074</v>
+      </c>
+      <c r="B7" t="n">
+        <v>92564</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>1339</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Brandticka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Pycnoporellus fulgens</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>öst om Östanås, Upl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>634874</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6699597</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Tolfta</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2021-10-18</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2021-10-18</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>örtrik äldre granskog</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>brunmurken granlåga</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Olof Hedgren</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Olof Hedgren</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>96736012</v>
+      </c>
+      <c r="B8" t="n">
+        <v>96338</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>2809</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Mörk husmossa</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hylocomiastrum umbratum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>öst om Östanås, Upl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>634793</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6699582</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Tolfta</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2021-10-15</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2021-10-15</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>örtrik äldre granskog</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Olof Hedgren</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Olof Hedgren</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>96736078</v>
+      </c>
+      <c r="B9" t="n">
+        <v>92632</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>öst om Östanås, Upl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>634836</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6699581</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Tolfta</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2021-10-18</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2021-10-18</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>örtrik äldre granskog</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>granlåga</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Olof Hedgren</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Olof Hedgren</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>102249941</v>
+      </c>
+      <c r="B10" t="n">
+        <v>6275</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>101520</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Större flatbagge</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Peltis grossa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Östanås, Upl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>634767</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6699623</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Tolfta</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2022-07-12</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2022-07-12</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Kläckhål på grov granhögstubbe med klibbticka. Även spår i klibbtickornas hymenium</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
           <t>Johan Lilja</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
+      <c r="AX10" t="inlineStr">
         <is>
           <t>Johan Lilja</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr">
+      <c r="AY10" t="inlineStr">
         <is>
           <t>Länsstyrelsen i Uppsala län, områdesskydd</t>
         </is>
       </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>102249952</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Östanås, Upl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>634679</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6700052</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Tolfta</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2022-07-12</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2022-07-12</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Johan Lilja</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Johan Lilja</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Uppsala län, områdesskydd</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>102249955</v>
+      </c>
+      <c r="B12" t="n">
+        <v>99096</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Östanås, Upl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>634657</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6700309</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Tolfta</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2022-07-12</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2022-07-12</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Johan Lilja</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Johan Lilja</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Uppsala län, områdesskydd</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>111057169</v>
+      </c>
+      <c r="B13" t="n">
+        <v>99096</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Östanås, Upl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>634674</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6700294</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Tolfta</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2022-11-07</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2022-11-07</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Karolina Bruce</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Douglas Skarp</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>102249951</v>
+      </c>
+      <c r="B14" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Östanås, Upl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>634653</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6700027</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Tolfta</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2022-07-12</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2022-07-12</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Johan Lilja</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Johan Lilja</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Uppsala län, områdesskydd</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>96736075</v>
+      </c>
+      <c r="B15" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>öst om Östanås, Upl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>634836</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6699581</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Tolfta</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2021-10-18</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2021-10-18</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>örtrik äldre granskog</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Olof Hedgren</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Olof Hedgren</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 73761-2021 artfynd.xlsx
+++ b/artfynd/A 73761-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AZ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96736156</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -885,6 +895,11 @@
           <t>Länsstyrelsen i Uppsala län, områdesskydd</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102249942</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -992,6 +1007,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96736011</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1099,6 +1119,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96736079</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1206,6 +1231,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96736081</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1313,6 +1343,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96736074</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1415,6 +1450,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96736012</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1522,6 +1562,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96736078</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1628,6 +1673,11 @@
           <t>Länsstyrelsen i Uppsala län, områdesskydd</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102249941</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1729,6 +1779,11 @@
           <t>Länsstyrelsen i Uppsala län, områdesskydd</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102249952</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1828,6 +1883,11 @@
       <c r="AY12" t="inlineStr">
         <is>
           <t>Länsstyrelsen i Uppsala län, områdesskydd</t>
+        </is>
+      </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102249955</t>
         </is>
       </c>
     </row>
@@ -1932,6 +1992,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111057169</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2033,6 +2098,11 @@
           <t>Länsstyrelsen i Uppsala län, områdesskydd</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102249951</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2140,8 +2210,29 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96736075</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>